--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_FUNDACIÓ CAIXA RURAL VILA-REAL.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_FUNDACIÓ CAIXA RURAL VILA-REAL.xlsx
@@ -565,13 +565,13 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>104.0338</v>
+        <v>97.295</v>
       </c>
       <c r="E2" t="n">
-        <v>61.4681</v>
+        <v>59.0534</v>
       </c>
       <c r="F2" t="n">
-        <v>42.5659</v>
+        <v>38.2417</v>
       </c>
       <c r="G2" t="n">
         <v>39.7314</v>
@@ -610,13 +610,13 @@
         <v>52.9612</v>
       </c>
       <c r="S2" t="n">
-        <v>32.4765</v>
+        <v>25.7371</v>
       </c>
       <c r="T2" t="n">
-        <v>13.5303</v>
+        <v>11.1154</v>
       </c>
       <c r="U2" t="n">
-        <v>18.9462</v>
+        <v>14.622</v>
       </c>
       <c r="V2" t="n">
         <v>23.0301</v>
@@ -643,13 +643,13 @@
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>93.1987</v>
+        <v>72.5363</v>
       </c>
       <c r="E3" t="n">
-        <v>51.4702</v>
+        <v>38.9724</v>
       </c>
       <c r="F3" t="n">
-        <v>41.7287</v>
+        <v>33.5633</v>
       </c>
       <c r="G3" t="n">
         <v>18.4925</v>
@@ -688,13 +688,13 @@
         <v>43.4316</v>
       </c>
       <c r="S3" t="n">
-        <v>52.5292</v>
+        <v>31.8671</v>
       </c>
       <c r="T3" t="n">
-        <v>26.0679</v>
+        <v>13.5706</v>
       </c>
       <c r="U3" t="n">
-        <v>26.4615</v>
+        <v>18.2962</v>
       </c>
       <c r="V3" t="n">
         <v>2.9349</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. IGBINS DAVID</t>
+          <t>A. CEJUDO GALÁN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>47.5217</v>
+        <v>40.9853</v>
       </c>
       <c r="E4" t="n">
-        <v>25.5817</v>
+        <v>40.9853</v>
       </c>
       <c r="F4" t="n">
-        <v>21.9402</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>19.3559</v>
+        <v>40.9853</v>
       </c>
       <c r="H4" t="n">
-        <v>17.2082</v>
+        <v>17.2307</v>
       </c>
       <c r="I4" t="n">
-        <v>2.1477</v>
+        <v>23.7541</v>
       </c>
       <c r="J4" t="n">
-        <v>25.8275</v>
+        <v>40.9853</v>
       </c>
       <c r="K4" t="n">
-        <v>20.1168</v>
+        <v>17.2307</v>
       </c>
       <c r="L4" t="n">
-        <v>5.710999999999999</v>
+        <v>23.7541</v>
       </c>
       <c r="M4" t="n">
-        <v>-6.471499999999999</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.9083</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-3.562900000000001</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-3.298700000000001</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-35.1856</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>31.8869</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>32.098</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>20.587</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>11.511</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.6337000000000002</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>14.3523</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-14.9859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>19</v>
       </c>
       <c r="D5" t="n">
-        <v>45.8105</v>
+        <v>38.68</v>
       </c>
       <c r="E5" t="n">
-        <v>31.3466</v>
+        <v>24.3427</v>
       </c>
       <c r="F5" t="n">
-        <v>14.4641</v>
+        <v>14.3374</v>
       </c>
       <c r="G5" t="n">
         <v>35.9514</v>
@@ -844,13 +844,13 @@
         <v>25.2892</v>
       </c>
       <c r="S5" t="n">
-        <v>23.1456</v>
+        <v>16.0149</v>
       </c>
       <c r="T5" t="n">
-        <v>15.4848</v>
+        <v>8.480599999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>7.6612</v>
+        <v>7.534000000000001</v>
       </c>
       <c r="V5" t="n">
         <v>-1.374700000000001</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. CEJUDO GALÁN</t>
+          <t>A. IGBINS DAVID</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,70 +874,70 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D6" t="n">
-        <v>40.9853</v>
+        <v>33.2566</v>
       </c>
       <c r="E6" t="n">
-        <v>40.9853</v>
+        <v>14.9515</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>18.3052</v>
       </c>
       <c r="G6" t="n">
-        <v>40.9853</v>
+        <v>19.3559</v>
       </c>
       <c r="H6" t="n">
-        <v>17.2307</v>
+        <v>17.2082</v>
       </c>
       <c r="I6" t="n">
-        <v>23.7541</v>
+        <v>2.1477</v>
       </c>
       <c r="J6" t="n">
-        <v>40.9853</v>
+        <v>25.8275</v>
       </c>
       <c r="K6" t="n">
-        <v>17.2307</v>
+        <v>20.1168</v>
       </c>
       <c r="L6" t="n">
-        <v>23.7541</v>
+        <v>5.710999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-6.471499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-2.9083</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-3.562900000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-3.298700000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-35.1856</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>31.8869</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>17.8331</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>9.956799999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>7.8761</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.6337000000000002</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>14.3523</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-14.9859</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>23</v>
       </c>
       <c r="D7" t="n">
-        <v>21.3439</v>
+        <v>26.7601</v>
       </c>
       <c r="E7" t="n">
-        <v>2.271599999999999</v>
+        <v>3.7014</v>
       </c>
       <c r="F7" t="n">
-        <v>19.0721</v>
+        <v>23.0586</v>
       </c>
       <c r="G7" t="n">
         <v>13.291</v>
@@ -1000,13 +1000,13 @@
         <v>41.2327</v>
       </c>
       <c r="S7" t="n">
-        <v>7.647600000000001</v>
+        <v>13.064</v>
       </c>
       <c r="T7" t="n">
-        <v>6.6062</v>
+        <v>8.0357</v>
       </c>
       <c r="U7" t="n">
-        <v>1.0416</v>
+        <v>5.0281</v>
       </c>
       <c r="V7" t="n">
         <v>1.1383</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. MORTE MONTAÑES</t>
+          <t>J. SABATE PRATS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D8" t="n">
-        <v>15.9289</v>
+        <v>25.4775</v>
       </c>
       <c r="E8" t="n">
-        <v>15.9289</v>
+        <v>10.0726</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>15.4049</v>
       </c>
       <c r="G8" t="n">
-        <v>15.9289</v>
+        <v>20.4619</v>
       </c>
       <c r="H8" t="n">
-        <v>7.8025</v>
+        <v>20.3946</v>
       </c>
       <c r="I8" t="n">
-        <v>8.126300000000001</v>
+        <v>0.06750000000000039</v>
       </c>
       <c r="J8" t="n">
-        <v>15.9289</v>
+        <v>33.528</v>
       </c>
       <c r="K8" t="n">
-        <v>7.8025</v>
+        <v>29.4812</v>
       </c>
       <c r="L8" t="n">
-        <v>8.126300000000001</v>
+        <v>4.046799999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>-13.0661</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-9.0868</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-3.9794</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-17.0428</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-40.3166</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>23.2737</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>7.6753</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.6086</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>7.0666</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>14.3832</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>16.2524</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.8693</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. SABATE PRATS</t>
+          <t>P. MORTE MONTAÑES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,70 +1108,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D9" t="n">
-        <v>15.1452</v>
+        <v>15.9289</v>
       </c>
       <c r="E9" t="n">
-        <v>1.925999999999999</v>
+        <v>15.9289</v>
       </c>
       <c r="F9" t="n">
-        <v>13.2193</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>20.4619</v>
+        <v>15.9289</v>
       </c>
       <c r="H9" t="n">
-        <v>20.3946</v>
+        <v>7.8025</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06750000000000039</v>
+        <v>8.126300000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>33.528</v>
+        <v>15.9289</v>
       </c>
       <c r="K9" t="n">
-        <v>29.4812</v>
+        <v>7.8025</v>
       </c>
       <c r="L9" t="n">
-        <v>4.046799999999999</v>
+        <v>8.126300000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-13.0661</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-9.0868</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-3.9794</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-17.0428</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-40.3166</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>23.2737</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.657100000000001</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-7.5381</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>4.8812</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>14.3832</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>16.2524</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.8693</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>10.4306</v>
+        <v>7.7517</v>
       </c>
       <c r="E10" t="n">
-        <v>8.972099999999999</v>
+        <v>6.115400000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4584</v>
+        <v>1.6363</v>
       </c>
       <c r="G10" t="n">
         <v>-4.5502</v>
@@ -1234,13 +1234,13 @@
         <v>9.1629</v>
       </c>
       <c r="S10" t="n">
-        <v>7.1778</v>
+        <v>4.4987</v>
       </c>
       <c r="T10" t="n">
-        <v>5.301</v>
+        <v>2.4443</v>
       </c>
       <c r="U10" t="n">
-        <v>1.8767</v>
+        <v>2.0546</v>
       </c>
       <c r="V10" t="n">
         <v>11.1015</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. LE BERRE CASTILLO</t>
+          <t>A. CEJUDO GALAN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,70 +1264,70 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="D11" t="n">
-        <v>3.99</v>
+        <v>7.436499999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2588000000000013</v>
+        <v>-7.101800000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>3.7313</v>
+        <v>14.5383</v>
       </c>
       <c r="G11" t="n">
-        <v>15.5909</v>
+        <v>16.8909</v>
       </c>
       <c r="H11" t="n">
-        <v>5.5259</v>
+        <v>10.0768</v>
       </c>
       <c r="I11" t="n">
-        <v>10.0649</v>
+        <v>6.814</v>
       </c>
       <c r="J11" t="n">
-        <v>17.776</v>
+        <v>21.6245</v>
       </c>
       <c r="K11" t="n">
-        <v>9.1197</v>
+        <v>14.1641</v>
       </c>
       <c r="L11" t="n">
-        <v>8.655899999999999</v>
+        <v>7.4604</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.185</v>
+        <v>-4.733600000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>-3.5938</v>
+        <v>-4.0872</v>
       </c>
       <c r="O11" t="n">
-        <v>1.4088</v>
+        <v>-0.6464999999999996</v>
       </c>
       <c r="P11" t="n">
-        <v>-5.6809</v>
+        <v>-7.330299999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>-19.6085</v>
+        <v>-47.0972</v>
       </c>
       <c r="R11" t="n">
-        <v>13.9275</v>
+        <v>39.7669</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5403000000000003</v>
+        <v>6.4165</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.0836</v>
+        <v>2.4606</v>
       </c>
       <c r="U11" t="n">
-        <v>1.5432</v>
+        <v>3.9559</v>
       </c>
       <c r="V11" t="n">
-        <v>-5.3793</v>
+        <v>-8.540800000000001</v>
       </c>
       <c r="W11" t="n">
-        <v>4.1749</v>
+        <v>15.91</v>
       </c>
       <c r="X11" t="n">
-        <v>-9.5543</v>
+        <v>-24.4507</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>15</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6292</v>
+        <v>6.621</v>
       </c>
       <c r="E12" t="n">
-        <v>3.6986</v>
+        <v>6.555899999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.0695</v>
+        <v>0.06510000000000007</v>
       </c>
       <c r="G12" t="n">
         <v>12.2029</v>
@@ -1390,13 +1390,13 @@
         <v>14.2941</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.9012</v>
+        <v>3.0908</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3082999999999999</v>
+        <v>2.5491</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.5928</v>
+        <v>0.5415</v>
       </c>
       <c r="V12" t="n">
         <v>-3.5414</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. NOS BARBERA</t>
+          <t>J. LE BERRE CASTILLO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.6420000000000002</v>
+        <v>6.390399999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.5575000000000002</v>
+        <v>2.2786</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.08449999999999996</v>
+        <v>4.1116</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9937</v>
+        <v>15.5909</v>
       </c>
       <c r="H13" t="n">
-        <v>2.3206</v>
+        <v>5.5259</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.3268</v>
+        <v>10.0649</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.3019999999999999</v>
+        <v>17.776</v>
       </c>
       <c r="K13" t="n">
-        <v>1.5697</v>
+        <v>9.1197</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.8716</v>
+        <v>8.655899999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>1.2954</v>
+        <v>-2.185</v>
       </c>
       <c r="N13" t="n">
-        <v>0.7508</v>
+        <v>-3.5938</v>
       </c>
       <c r="O13" t="n">
-        <v>0.5446000000000001</v>
+        <v>1.4088</v>
       </c>
       <c r="P13" t="n">
-        <v>0.7331</v>
+        <v>-5.6809</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9163</v>
+        <v>-19.6085</v>
       </c>
       <c r="R13" t="n">
-        <v>1.6494</v>
+        <v>13.9275</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4579</v>
+        <v>1.8599</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6064000000000001</v>
+        <v>-0.06359999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1486</v>
+        <v>1.9235</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.9109</v>
+        <v>-5.3793</v>
       </c>
       <c r="W13" t="n">
-        <v>1.267</v>
+        <v>4.1749</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.1779</v>
+        <v>-9.5543</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>V. RUBERT BALLESTER</t>
+          <t>J. VILLAR SOLER</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.2321</v>
+        <v>4.286</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.1156</v>
+        <v>-7.9475</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1166</v>
+        <v>12.2335</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.2635</v>
+        <v>-12.5843</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.8019999999999999</v>
+        <v>-3.0552</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4616000000000001</v>
+        <v>-9.528599999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.1337</v>
+        <v>-1.2655</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.5760999999999999</v>
+        <v>10.2136</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.5577000000000001</v>
+        <v>-11.4794</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1298</v>
+        <v>-11.3186</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2259</v>
+        <v>-13.2689</v>
       </c>
       <c r="O14" t="n">
-        <v>0.09610000000000002</v>
+        <v>1.950800000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7331</v>
+        <v>16.6765</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-12.2785</v>
       </c>
       <c r="R14" t="n">
-        <v>0.7331</v>
+        <v>28.9547</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7015</v>
+        <v>4.2437</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0181</v>
+        <v>1.1208</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7197</v>
+        <v>3.1236</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-4.05</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>4.476</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-8.5261</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. GARCIA GARCIA</t>
+          <t>M. NOS BARBERA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.9802</v>
+        <v>0.1416999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.3981</v>
+        <v>-0.02169999999999983</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.5821</v>
+        <v>0.1633</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.8421</v>
+        <v>0.9937</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.1563</v>
+        <v>2.3206</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3142999999999999</v>
+        <v>-1.3268</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.1581</v>
+        <v>-0.3019999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.152</v>
+        <v>1.5697</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.006000000000000005</v>
+        <v>-1.8716</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.6840000000000001</v>
+        <v>1.2954</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0043</v>
+        <v>0.7508</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3203</v>
+        <v>0.5446000000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5498</v>
+        <v>0.7331</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.1833</v>
+        <v>-0.9163</v>
       </c>
       <c r="R15" t="n">
-        <v>0.7331</v>
+        <v>1.6494</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5687</v>
+        <v>0.3257</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9328</v>
+        <v>-0.0704</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3642</v>
+        <v>0.3962</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.2565</v>
+        <v>-1.9109</v>
       </c>
       <c r="W15" t="n">
-        <v>0.01040000000000002</v>
+        <v>1.267</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.267</v>
+        <v>-3.1779</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. VILLAR SOLER</t>
+          <t>M. MARIA VENTURA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D16" t="n">
-        <v>-6.8999</v>
+        <v>-0.4613999999999994</v>
       </c>
       <c r="E16" t="n">
-        <v>-14.268</v>
+        <v>-5.271700000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>7.3681</v>
+        <v>4.8102</v>
       </c>
       <c r="G16" t="n">
-        <v>-12.5843</v>
+        <v>-2.9794</v>
       </c>
       <c r="H16" t="n">
-        <v>-3.0552</v>
+        <v>5.7322</v>
       </c>
       <c r="I16" t="n">
-        <v>-9.528599999999999</v>
+        <v>-8.7119</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.2655</v>
+        <v>2.950199999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>10.2136</v>
+        <v>6.0488</v>
       </c>
       <c r="L16" t="n">
-        <v>-11.4794</v>
+        <v>-3.0983</v>
       </c>
       <c r="M16" t="n">
-        <v>-11.3186</v>
+        <v>-5.9297</v>
       </c>
       <c r="N16" t="n">
-        <v>-13.2689</v>
+        <v>-0.3163999999999998</v>
       </c>
       <c r="O16" t="n">
-        <v>1.950800000000001</v>
+        <v>-5.6135</v>
       </c>
       <c r="P16" t="n">
-        <v>16.6765</v>
+        <v>5.6812</v>
       </c>
       <c r="Q16" t="n">
-        <v>-12.2785</v>
+        <v>-17.4097</v>
       </c>
       <c r="R16" t="n">
-        <v>28.9547</v>
+        <v>23.0907</v>
       </c>
       <c r="S16" t="n">
-        <v>-6.9423</v>
+        <v>5.0933</v>
       </c>
       <c r="T16" t="n">
-        <v>-5.2003</v>
+        <v>3.4444</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.742</v>
+        <v>1.6489</v>
       </c>
       <c r="V16" t="n">
-        <v>-4.05</v>
+        <v>-8.2562</v>
       </c>
       <c r="W16" t="n">
-        <v>4.476</v>
+        <v>5.7427</v>
       </c>
       <c r="X16" t="n">
-        <v>-8.5261</v>
+        <v>-13.9989</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. MARIA VENTURA</t>
+          <t>V. RUBERT BALLESTER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>-10.1831</v>
+        <v>-0.7732</v>
       </c>
       <c r="E17" t="n">
-        <v>-10.9044</v>
+        <v>-0.7308999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7213000000000005</v>
+        <v>-0.04220000000000002</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.9794</v>
+        <v>-1.2635</v>
       </c>
       <c r="H17" t="n">
-        <v>5.7322</v>
+        <v>-0.8019999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>-8.7119</v>
+        <v>-0.4616000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>2.950199999999999</v>
+        <v>-1.1337</v>
       </c>
       <c r="K17" t="n">
-        <v>6.0488</v>
+        <v>-0.5760999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>-3.0983</v>
+        <v>-0.5577000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>-5.9297</v>
+        <v>-0.1298</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3163999999999998</v>
+        <v>-0.2259</v>
       </c>
       <c r="O17" t="n">
-        <v>-5.6135</v>
+        <v>0.09610000000000002</v>
       </c>
       <c r="P17" t="n">
-        <v>5.6812</v>
+        <v>0.7331</v>
       </c>
       <c r="Q17" t="n">
-        <v>-17.4097</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>23.0907</v>
+        <v>0.7331</v>
       </c>
       <c r="S17" t="n">
-        <v>-4.6286</v>
+        <v>-0.2427</v>
       </c>
       <c r="T17" t="n">
-        <v>-2.1882</v>
+        <v>0.4028</v>
       </c>
       <c r="U17" t="n">
-        <v>-2.4403</v>
+        <v>-0.6453</v>
       </c>
       <c r="V17" t="n">
-        <v>-8.2562</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>5.7427</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-13.9989</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. CEJUDO GALAN</t>
+          <t>M. GARCIA GARCIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>-10.5778</v>
+        <v>-2.1279</v>
       </c>
       <c r="E18" t="n">
-        <v>-18.9451</v>
+        <v>-0.7686999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>8.3674</v>
+        <v>-1.3592</v>
       </c>
       <c r="G18" t="n">
-        <v>16.8909</v>
+        <v>-1.8421</v>
       </c>
       <c r="H18" t="n">
-        <v>10.0768</v>
+        <v>-2.1563</v>
       </c>
       <c r="I18" t="n">
-        <v>6.814</v>
+        <v>0.3142999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>21.6245</v>
+        <v>-1.1581</v>
       </c>
       <c r="K18" t="n">
-        <v>14.1641</v>
+        <v>-1.152</v>
       </c>
       <c r="L18" t="n">
-        <v>7.4604</v>
+        <v>-0.006000000000000005</v>
       </c>
       <c r="M18" t="n">
-        <v>-4.733600000000001</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>-4.0872</v>
+        <v>-1.0043</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6464999999999996</v>
+        <v>0.3203</v>
       </c>
       <c r="P18" t="n">
-        <v>-7.330299999999999</v>
+        <v>0.5498</v>
       </c>
       <c r="Q18" t="n">
-        <v>-47.0972</v>
+        <v>-0.1833</v>
       </c>
       <c r="R18" t="n">
-        <v>39.7669</v>
+        <v>0.7331</v>
       </c>
       <c r="S18" t="n">
-        <v>-11.5975</v>
+        <v>0.421</v>
       </c>
       <c r="T18" t="n">
-        <v>-9.382400000000001</v>
+        <v>0.5622</v>
       </c>
       <c r="U18" t="n">
-        <v>-2.215</v>
+        <v>-0.1412</v>
       </c>
       <c r="V18" t="n">
-        <v>-8.540800000000001</v>
+        <v>-1.2565</v>
       </c>
       <c r="W18" t="n">
-        <v>15.91</v>
+        <v>0.01040000000000002</v>
       </c>
       <c r="X18" t="n">
-        <v>-24.4507</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. PEREZ RIPOLL</t>
+          <t>G. VOLPATO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,76 +1888,76 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D19" t="n">
-        <v>-17.8147</v>
+        <v>-13.3555</v>
       </c>
       <c r="E19" t="n">
-        <v>-15.1727</v>
+        <v>-9.4133</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.642</v>
+        <v>-3.942299999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>-10.3754</v>
+        <v>-13.9167</v>
       </c>
       <c r="H19" t="n">
-        <v>-5.7113</v>
+        <v>0.5177</v>
       </c>
       <c r="I19" t="n">
-        <v>-4.6639</v>
+        <v>-14.4343</v>
       </c>
       <c r="J19" t="n">
-        <v>-5.1036</v>
+        <v>-9.354900000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.7825</v>
+        <v>2.8018</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.3213</v>
+        <v>-12.1569</v>
       </c>
       <c r="M19" t="n">
-        <v>-5.2713</v>
+        <v>-4.5616</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.9287</v>
+        <v>-2.2841</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.3427</v>
+        <v>-2.2774</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3824</v>
+        <v>8.796199999999999</v>
       </c>
       <c r="Q19" t="n">
-        <v>-15.7603</v>
+        <v>-2.9322</v>
       </c>
       <c r="R19" t="n">
-        <v>18.1426</v>
+        <v>11.7284</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.4587</v>
+        <v>-0.9450000000000002</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0074</v>
+        <v>0.9732999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.4515</v>
+        <v>-1.9184</v>
       </c>
       <c r="V19" t="n">
-        <v>-7.3633</v>
+        <v>-7.2903</v>
       </c>
       <c r="W19" t="n">
-        <v>6.6982</v>
+        <v>1.9005</v>
       </c>
       <c r="X19" t="n">
-        <v>-14.0616</v>
+        <v>-9.1907</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. VOLPATO</t>
+          <t>A. PEREZ RIPOLL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,70 +1966,70 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D20" t="n">
-        <v>-18.9887</v>
+        <v>-14.0405</v>
       </c>
       <c r="E20" t="n">
-        <v>-13.3284</v>
+        <v>-12.5755</v>
       </c>
       <c r="F20" t="n">
-        <v>-5.6602</v>
+        <v>-1.4648</v>
       </c>
       <c r="G20" t="n">
-        <v>-13.9167</v>
+        <v>-10.3754</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5177</v>
+        <v>-5.7113</v>
       </c>
       <c r="I20" t="n">
-        <v>-14.4343</v>
+        <v>-4.6639</v>
       </c>
       <c r="J20" t="n">
-        <v>-9.354900000000001</v>
+        <v>-5.1036</v>
       </c>
       <c r="K20" t="n">
-        <v>2.8018</v>
+        <v>-2.7825</v>
       </c>
       <c r="L20" t="n">
-        <v>-12.1569</v>
+        <v>-2.3213</v>
       </c>
       <c r="M20" t="n">
-        <v>-4.5616</v>
+        <v>-5.2713</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.2841</v>
+        <v>-2.9287</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.2774</v>
+        <v>-2.3427</v>
       </c>
       <c r="P20" t="n">
-        <v>8.796199999999999</v>
+        <v>2.3824</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.9322</v>
+        <v>-15.7603</v>
       </c>
       <c r="R20" t="n">
-        <v>11.7284</v>
+        <v>18.1426</v>
       </c>
       <c r="S20" t="n">
-        <v>-6.5785</v>
+        <v>1.3154</v>
       </c>
       <c r="T20" t="n">
-        <v>-2.9418</v>
+        <v>1.5896</v>
       </c>
       <c r="U20" t="n">
-        <v>-3.6364</v>
+        <v>-0.2738</v>
       </c>
       <c r="V20" t="n">
-        <v>-7.2903</v>
+        <v>-7.3633</v>
       </c>
       <c r="W20" t="n">
-        <v>1.9005</v>
+        <v>6.6982</v>
       </c>
       <c r="X20" t="n">
-        <v>-9.1907</v>
+        <v>-14.0616</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>26</v>
       </c>
       <c r="D21" t="n">
-        <v>330.6992999999999</v>
+        <v>352.7884999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>169.2181</v>
+        <v>179.127</v>
       </c>
       <c r="F21" t="n">
-        <v>161.4819</v>
+        <v>173.6609</v>
       </c>
       <c r="G21" t="n">
         <v>202.3651</v>
@@ -2062,7 +2062,7 @@
         <v>173.6639</v>
       </c>
       <c r="I21" t="n">
-        <v>28.7017</v>
+        <v>28.70170000000001</v>
       </c>
       <c r="J21" t="n">
         <v>318.3431</v>
@@ -2071,7 +2071,7 @@
         <v>251.9164</v>
       </c>
       <c r="L21" t="n">
-        <v>66.4255</v>
+        <v>66.42550000000001</v>
       </c>
       <c r="M21" t="n">
         <v>-115.9765</v>
@@ -2083,25 +2083,25 @@
         <v>-37.724</v>
       </c>
       <c r="P21" t="n">
-        <v>9.163</v>
+        <v>9.162999999999997</v>
       </c>
       <c r="Q21" t="n">
         <v>-371.0981</v>
       </c>
       <c r="R21" t="n">
-        <v>380.2587000000001</v>
+        <v>380.2587</v>
       </c>
       <c r="S21" t="n">
-        <v>116.1798</v>
+        <v>138.2688</v>
       </c>
       <c r="T21" t="n">
-        <v>57.2716</v>
+        <v>67.1808</v>
       </c>
       <c r="U21" t="n">
-        <v>58.90929999999999</v>
+        <v>71.0885</v>
       </c>
       <c r="V21" t="n">
-        <v>2.990899999999995</v>
+        <v>2.990899999999997</v>
       </c>
       <c r="W21" t="n">
         <v>164.698</v>
